--- a/daily_matches/job_matches_2026-04-18.xlsx
+++ b/daily_matches/job_matches_2026-04-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,340 +468,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineer/ Sr Engineer, IT AI</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Keras, BigQuery, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd18edcb36ac9a04</t>
+          <t>https://www.indeed.com/viewjob?jk=c69e0cd00bf5d75b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Sr Cloud Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Personify Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, S3, EC2, Glue, Redshift, Kinesis, Docker, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84f96f202d778253</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e55d4c15c9b5aa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>AI/ML Engineer - GCP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Data Sherpas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, BigQuery, Data Lake, Dataflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2618c9f668eecbb</t>
+          <t>https://www.indeed.com/viewjob?jk=0430c385b75499a0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>PyTorch, XGBoost, Azure ML, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4db56fc9e099e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc1792488693d8a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Machine Learning Engineer II Recommendation Systems- Credit Karma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Keras, BigQuery, Dataflow, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcfc317f07ec3caa</t>
+          <t>https://www.indeed.com/viewjob?jk=c95ddf0fac17d5df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Fullstack Developer (contract)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c44539ed64115952</t>
+          <t>https://www.indeed.com/viewjob?jk=78b2b7e09c674466</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Integration Engineer</t>
+          <t>Full stack - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=098d9fe6c69049e5</t>
+          <t>https://www.indeed.com/viewjob?jk=75ddd2ef066cb6c7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72d6efe907b7366e</t>
+          <t>https://www.indeed.com/viewjob?jk=51a155a2ec6a3efc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Senior Software Engineer - Production Control Plane</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a44ecb1dd02fe6fc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5919ca76700b393</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Experienced Associate - AI Native Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Gemini, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28739fe08c3eac0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a44496f4ad332ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Experienced Associate - AI Native Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Gemini, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03c4608a1787de15</t>
+          <t>https://www.indeed.com/viewjob?jk=62dbf135d3838d78</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer, Presentation and Visual Optimization</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>Paramount Streaming</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eca9c2208420492</t>
+          <t>https://www.indeed.com/viewjob?jk=a25d70a2f2c4a95d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, BigQuery, Dataflow, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a00846a02b4b2ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a4ef0f67995896f6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applied AI</t>
+          <t>AI Engineer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Git, Snowflake</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Azure ML, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358628d1d9d8926f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0478d80994fcab6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer, Applied AI</t>
+          <t>Conservancy Data Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Chesapeake Conservancy Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Git, Snowflake</t>
+          <t>RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Java, Bayesian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee746e768276b209</t>
+          <t>https://www.indeed.com/viewjob?jk=deb663576b9fc6e8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Data Scientist Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GumGum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, PyTorch, OpenCV, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb4946c0d6f0626</t>
+          <t>https://www.indeed.com/viewjob?jk=cee648c0a51f09de</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Frontend/React</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, SQL</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43792765a0db7bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=9e581126e800334e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full stack Software Engineer</t>
+          <t>Senior Data Platform Engineer (Data and Analytics Cloud Engineer)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a606aed8d9f40168</t>
+          <t>https://www.indeed.com/viewjob?jk=9bcac59d962ae37d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Sr. Software Developer - Platform Engineering Hybrid or Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pros.</t>
+          <t>Redfin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, Databricks, PySpark, Python, R</t>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,707 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa6e20dd3b71f73b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Schaumburg, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2cb75fadfe176f</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, AWS SageMaker, Docker, Kubernetes, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2025-12-23</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58885977f22c9b8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, AWS SageMaker, Docker, Kubernetes, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6c55d21db673bf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Cybersecurity Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, AWS SageMaker, Docker, Kubernetes, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f78f60d3db5a3ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Xsolis</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Franklin, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AKS, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfc2f5ebc540e0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Analytics Engineer III (Microsoft Fabric, Power BI)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Children's Health</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5463959d582cb8c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11ed9ed533b0e215</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack Java/React) - Commissions Platform - HYBRID</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe546327480c369</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Data Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Paychex, Inc.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d4f02634055cba</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Data Society</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8fffe50fd8d0ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Scientist – NLP &amp; Gen AI</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>DATAMAXIS</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Python, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ceb8d5385226e58</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Front End UI Developer (Angular)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>CI/CD, Jenkins, Git, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2894d188b4dc4e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Engineer, DevOps (R4819)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Shield AI</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8634183b27cd9fe3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Sr. Software Developer - Platform Engineering Hybrid or Remote</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Redfin</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d31f8b67346f7f08</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>IT Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>t1 energy</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688ce8f0a2ba3987</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>GTM Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>DemandDrive</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, AKS, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccfead9ae273659d</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Insights &amp; Integrations Consultancy Data Scientist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Geotab</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ecddba5baf356c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>AI Solutions Specialist</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Shook, Hardy &amp; Bacon LLP</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Power BI, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae45cb4a27c53669</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>MedReview</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da41115417ca40ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>AI Intern</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Aspire Tech IT Solution</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Middletown, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, TensorFlow, PyTorch, Docker, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=353badde2f3ac9be</t>
+          <t>https://www.indeed.com/viewjob?jk=17621d2f2aa0892a</t>
         </is>
       </c>
     </row>
